--- a/weights/baseline_results.xlsx
+++ b/weights/baseline_results.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,607 +417,607 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Avg_0.4</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Std_0.4</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Min_0.4</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Max_0.4</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Avg_0.45</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Std_0.45</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Min_0.45</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Max_0.45</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Avg_0.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Std_0.5</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Min_0.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Max_0.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Avg_0.54</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Std_0.54</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Min_0.54</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Max_0.54</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Avg_0.59</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Std_0.59</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Min_0.59</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Max_0.59</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Avg_0.64</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Std_0.64</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Min_0.64</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Max_0.64</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Avg_0.69</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Std_0.69</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Min_0.69</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Max_0.69</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Avg_0.74</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Std_0.74</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Min_0.74</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>Max_0.74</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>Avg_0.79</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>Std_0.79</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>Min_0.79</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>Max_0.79</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>Avg_0.83</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>Std_0.83</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>Min_0.83</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>Max_0.83</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>Avg_0.88</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>Std_0.88</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>Min_0.88</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>Max_0.88</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>Avg_0.93</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>Std_0.93</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Min_0.93</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>Max_0.93</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>Avg_0.98</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>Std_0.98</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>Min_0.98</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>Max_0.98</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>Avg_1.03</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>Std_1.03</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>Min_1.03</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>Max_1.03</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>Avg_1.08</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>Std_1.08</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>Min_1.08</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>Max_1.08</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>Avg_1.12</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>Std_1.12</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>Min_1.12</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>Max_1.12</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>Avg_1.17</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>Std_1.17</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>Min_1.17</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>Max_1.17</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>Avg_1.22</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>Std_1.22</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>Min_1.22</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>Max_1.22</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>Avg_1.27</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>Std_1.27</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>Min_1.27</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>Max_1.27</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>Avg_1.32</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>Std_1.32</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>Min_1.32</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>Max_1.32</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>Avg_1.37</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>Std_1.37</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>Min_1.37</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>Max_1.37</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>Avg_1.41</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>Std_1.41</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>Min_1.41</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>Max_1.41</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>Avg_1.46</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>Std_1.46</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>Min_1.46</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>Max_1.46</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>Avg_1.51</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>Std_1.51</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>Min_1.51</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>Max_1.51</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>Avg_1.56</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>Std_1.56</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>Min_1.56</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>Max_1.56</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>Avg_1.61</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>Std_1.61</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>Min_1.61</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>Max_1.61</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>Avg_1.66</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>Std_1.66</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>Min_1.66</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>Max_1.66</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>Avg_1.7</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>Std_1.7</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>Min_1.7</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>Max_1.7</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>Avg_1.75</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>Std_1.75</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>Min_1.75</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>Max_1.75</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>Avg_1.8</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>Std_1.8</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>Min_1.8</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>Max_1.8</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>Total_Avg</t>
         </is>
@@ -1037,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>244.1</v>
+        <v>409.3</v>
       </c>
       <c r="B2" t="n">
-        <v>3.269556544854363</v>
+        <v>131.0114880458962</v>
       </c>
       <c r="C2" t="n">
-        <v>236</v>
+        <v>100</v>
       </c>
       <c r="D2" t="n">
-        <v>248</v>
+        <v>678</v>
       </c>
       <c r="E2" t="n">
-        <v>244.2</v>
+        <v>430.1</v>
       </c>
       <c r="F2" t="n">
-        <v>3.370459909270543</v>
+        <v>23.80105039698878</v>
       </c>
       <c r="G2" t="n">
-        <v>239</v>
+        <v>389</v>
       </c>
       <c r="H2" t="n">
-        <v>251</v>
+        <v>473</v>
       </c>
       <c r="I2" t="n">
-        <v>242.7</v>
+        <v>426.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.716180835212409</v>
+        <v>15.25417975507041</v>
       </c>
       <c r="K2" t="n">
-        <v>236</v>
+        <v>402</v>
       </c>
       <c r="L2" t="n">
-        <v>251</v>
+        <v>457</v>
       </c>
       <c r="M2" t="n">
-        <v>247.2</v>
+        <v>428.1</v>
       </c>
       <c r="N2" t="n">
-        <v>4.489988864128729</v>
+        <v>9.761659694949419</v>
       </c>
       <c r="O2" t="n">
-        <v>242</v>
+        <v>412</v>
       </c>
       <c r="P2" t="n">
-        <v>256</v>
+        <v>442</v>
       </c>
       <c r="Q2" t="n">
-        <v>245.7</v>
+        <v>360.2</v>
       </c>
       <c r="R2" t="n">
-        <v>8.474078120952155</v>
+        <v>128.5050971751704</v>
       </c>
       <c r="S2" t="n">
-        <v>231</v>
+        <v>102</v>
       </c>
       <c r="T2" t="n">
-        <v>257</v>
+        <v>439</v>
       </c>
       <c r="U2" t="n">
-        <v>241.9</v>
+        <v>394.8</v>
       </c>
       <c r="V2" t="n">
-        <v>8.178630692236936</v>
+        <v>96.93791827762757</v>
       </c>
       <c r="W2" t="n">
-        <v>226</v>
+        <v>105</v>
       </c>
       <c r="X2" t="n">
-        <v>257</v>
+        <v>443</v>
       </c>
       <c r="Y2" t="n">
-        <v>236.7</v>
+        <v>267.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.40173600646811</v>
+        <v>162.5996309958912</v>
       </c>
       <c r="AA2" t="n">
-        <v>221</v>
+        <v>101</v>
       </c>
       <c r="AB2" t="n">
-        <v>264</v>
+        <v>445</v>
       </c>
       <c r="AC2" t="n">
-        <v>236.6</v>
+        <v>266.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.531002045955084</v>
+        <v>163.7968558916807</v>
       </c>
       <c r="AE2" t="n">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="AF2" t="n">
-        <v>254</v>
+        <v>443</v>
       </c>
       <c r="AG2" t="n">
-        <v>235.9</v>
+        <v>267.3</v>
       </c>
       <c r="AH2" t="n">
-        <v>11.18436408563312</v>
+        <v>164.3733859236342</v>
       </c>
       <c r="AI2" t="n">
-        <v>214</v>
+        <v>99</v>
       </c>
       <c r="AJ2" t="n">
-        <v>253</v>
+        <v>440</v>
       </c>
       <c r="AK2" t="n">
-        <v>243</v>
+        <v>300</v>
       </c>
       <c r="AL2" t="n">
-        <v>14.34573107234344</v>
+        <v>161.1291407536204</v>
       </c>
       <c r="AM2" t="n">
-        <v>225</v>
+        <v>99</v>
       </c>
       <c r="AN2" t="n">
-        <v>269</v>
+        <v>442</v>
       </c>
       <c r="AO2" t="n">
-        <v>232.9</v>
+        <v>169.9</v>
       </c>
       <c r="AP2" t="n">
-        <v>12.1280666225083</v>
+        <v>131.8639071163903</v>
       </c>
       <c r="AQ2" t="n">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="AR2" t="n">
-        <v>264</v>
+        <v>437</v>
       </c>
       <c r="AS2" t="n">
-        <v>239.4</v>
+        <v>138.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>13.88668426947196</v>
+        <v>99.31168108535874</v>
       </c>
       <c r="AU2" t="n">
-        <v>224</v>
+        <v>98</v>
       </c>
       <c r="AV2" t="n">
-        <v>267</v>
+        <v>436</v>
       </c>
       <c r="AW2" t="n">
-        <v>244.6</v>
+        <v>134</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.10106378965786</v>
+        <v>99.70957827611147</v>
       </c>
       <c r="AY2" t="n">
-        <v>225</v>
+        <v>96</v>
       </c>
       <c r="AZ2" t="n">
-        <v>266</v>
+        <v>433</v>
       </c>
       <c r="BA2" t="n">
-        <v>237.1</v>
+        <v>104.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>13.53107534529314</v>
+        <v>6.624952830020754</v>
       </c>
       <c r="BC2" t="n">
-        <v>222</v>
+        <v>96</v>
       </c>
       <c r="BD2" t="n">
-        <v>259</v>
+        <v>113</v>
       </c>
       <c r="BE2" t="n">
-        <v>241.3</v>
+        <v>107</v>
       </c>
       <c r="BF2" t="n">
-        <v>15.23187447427269</v>
+        <v>11.15347479487895</v>
       </c>
       <c r="BG2" t="n">
-        <v>221</v>
+        <v>97</v>
       </c>
       <c r="BH2" t="n">
-        <v>263</v>
+        <v>137</v>
       </c>
       <c r="BI2" t="n">
-        <v>244.8</v>
+        <v>103.1</v>
       </c>
       <c r="BJ2" t="n">
-        <v>16.01749044014074</v>
+        <v>4.482186966202994</v>
       </c>
       <c r="BK2" t="n">
-        <v>219</v>
+        <v>97</v>
       </c>
       <c r="BL2" t="n">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="BM2" t="n">
-        <v>250.7</v>
+        <v>106.7</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.165225056719341</v>
+        <v>6.148983655857283</v>
       </c>
       <c r="BO2" t="n">
-        <v>242</v>
+        <v>99</v>
       </c>
       <c r="BP2" t="n">
-        <v>263</v>
+        <v>118</v>
       </c>
       <c r="BQ2" t="n">
-        <v>239.3</v>
+        <v>113.7</v>
       </c>
       <c r="BR2" t="n">
-        <v>17.01205454964214</v>
+        <v>11.33181362359971</v>
       </c>
       <c r="BS2" t="n">
-        <v>218</v>
+        <v>99</v>
       </c>
       <c r="BT2" t="n">
-        <v>277</v>
+        <v>129</v>
       </c>
       <c r="BU2" t="n">
-        <v>240.3</v>
+        <v>121.4</v>
       </c>
       <c r="BV2" t="n">
-        <v>20.96687864227768</v>
+        <v>17.77188791321845</v>
       </c>
       <c r="BW2" t="n">
-        <v>213</v>
+        <v>99</v>
       </c>
       <c r="BX2" t="n">
-        <v>276</v>
+        <v>153</v>
       </c>
       <c r="BY2" t="n">
-        <v>234.9</v>
+        <v>123.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11.59698236611577</v>
+        <v>25.78449146289296</v>
       </c>
       <c r="CA2" t="n">
-        <v>216</v>
+        <v>98</v>
       </c>
       <c r="CB2" t="n">
-        <v>257</v>
+        <v>161</v>
       </c>
       <c r="CC2" t="n">
-        <v>232.2</v>
+        <v>134.8</v>
       </c>
       <c r="CD2" t="n">
-        <v>15.44538766104626</v>
+        <v>30.37696495701965</v>
       </c>
       <c r="CE2" t="n">
-        <v>216</v>
+        <v>102</v>
       </c>
       <c r="CF2" t="n">
-        <v>263</v>
+        <v>175</v>
       </c>
       <c r="CG2" t="n">
-        <v>397.7</v>
+        <v>154.8</v>
       </c>
       <c r="CH2" t="n">
-        <v>382.8858968413435</v>
+        <v>20.85569466596594</v>
       </c>
       <c r="CI2" t="n">
-        <v>222</v>
+        <v>103</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1523</v>
+        <v>174</v>
       </c>
       <c r="CK2" t="n">
-        <v>408.5</v>
+        <v>155.5</v>
       </c>
       <c r="CL2" t="n">
-        <v>396.6376810137938</v>
+        <v>18.51620911525899</v>
       </c>
       <c r="CM2" t="n">
-        <v>193</v>
+        <v>102</v>
       </c>
       <c r="CN2" t="n">
-        <v>1550</v>
+        <v>169</v>
       </c>
       <c r="CO2" t="n">
-        <v>658.4</v>
+        <v>133.3</v>
       </c>
       <c r="CP2" t="n">
-        <v>538.5393578931812</v>
+        <v>28.64280014244418</v>
       </c>
       <c r="CQ2" t="n">
-        <v>192</v>
+        <v>86</v>
       </c>
       <c r="CR2" t="n">
-        <v>1558</v>
+        <v>159</v>
       </c>
       <c r="CS2" t="n">
-        <v>434.7</v>
+        <v>137.2</v>
       </c>
       <c r="CT2" t="n">
-        <v>266.9734256438269</v>
+        <v>26.26708967510485</v>
       </c>
       <c r="CU2" t="n">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="CV2" t="n">
-        <v>1045</v>
+        <v>158</v>
       </c>
       <c r="CW2" t="n">
-        <v>423.5</v>
+        <v>143.1</v>
       </c>
       <c r="CX2" t="n">
-        <v>300.7774093910645</v>
+        <v>12.259282197584</v>
       </c>
       <c r="CY2" t="n">
-        <v>190</v>
+        <v>117</v>
       </c>
       <c r="CZ2" t="n">
-        <v>989</v>
+        <v>152</v>
       </c>
       <c r="DA2" t="n">
-        <v>296.8</v>
+        <v>124.3</v>
       </c>
       <c r="DB2" t="n">
-        <v>133.111081432013</v>
+        <v>19.24603855342704</v>
       </c>
       <c r="DC2" t="n">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="DD2" t="n">
-        <v>561</v>
+        <v>150</v>
       </c>
       <c r="DE2" t="n">
-        <v>246.7</v>
+        <v>133.8</v>
       </c>
       <c r="DF2" t="n">
-        <v>60.4450990569128</v>
+        <v>12.57616793780999</v>
       </c>
       <c r="DG2" t="n">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="DH2" t="n">
-        <v>408</v>
+        <v>148</v>
       </c>
       <c r="DI2" t="n">
-        <v>241.5</v>
+        <v>114.9</v>
       </c>
       <c r="DJ2" t="n">
-        <v>68.05181849149955</v>
+        <v>13.41976154780703</v>
       </c>
       <c r="DK2" t="n">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="DL2" t="n">
-        <v>434</v>
+        <v>140</v>
       </c>
       <c r="DM2" t="n">
-        <v>253.2</v>
+        <v>118.5</v>
       </c>
       <c r="DN2" t="n">
-        <v>118.7634623947955</v>
+        <v>9.82089608946149</v>
       </c>
       <c r="DO2" t="n">
-        <v>187</v>
+        <v>98</v>
       </c>
       <c r="DP2" t="n">
-        <v>603</v>
+        <v>135</v>
       </c>
       <c r="DQ2" t="n">
-        <v>8416.5</v>
+        <v>6122.400000000001</v>
       </c>
     </row>
   </sheetData>

--- a/weights/baseline_results.xlsx
+++ b/weights/baseline_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>409.3</v>
+        <v>124.5</v>
       </c>
       <c r="B2" t="n">
-        <v>131.0114880458962</v>
+        <v>17.70451919708638</v>
       </c>
       <c r="C2" t="n">
+        <v>103</v>
+      </c>
+      <c r="D2" t="n">
+        <v>163</v>
+      </c>
+      <c r="E2" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.02131818450032</v>
+      </c>
+      <c r="G2" t="n">
+        <v>101</v>
+      </c>
+      <c r="H2" t="n">
+        <v>144</v>
+      </c>
+      <c r="I2" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>19.10732843701599</v>
+      </c>
+      <c r="K2" t="n">
+        <v>99</v>
+      </c>
+      <c r="L2" t="n">
+        <v>157</v>
+      </c>
+      <c r="M2" t="n">
+        <v>204</v>
+      </c>
+      <c r="N2" t="n">
+        <v>268.2189404199487</v>
+      </c>
+      <c r="O2" t="n">
+        <v>101</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="R2" t="n">
+        <v>50.66201733054064</v>
+      </c>
+      <c r="S2" t="n">
+        <v>101</v>
+      </c>
+      <c r="T2" t="n">
+        <v>271</v>
+      </c>
+      <c r="U2" t="n">
+        <v>400.6</v>
+      </c>
+      <c r="V2" t="n">
+        <v>421.9889098068811</v>
+      </c>
+      <c r="W2" t="n">
+        <v>102</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>225.8</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>272.5783557071251</v>
+      </c>
+      <c r="AA2" t="n">
         <v>100</v>
       </c>
-      <c r="D2" t="n">
-        <v>678</v>
-      </c>
-      <c r="E2" t="n">
-        <v>430.1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>23.80105039698878</v>
-      </c>
-      <c r="G2" t="n">
-        <v>389</v>
-      </c>
-      <c r="H2" t="n">
-        <v>473</v>
-      </c>
-      <c r="I2" t="n">
-        <v>426.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15.25417975507041</v>
-      </c>
-      <c r="K2" t="n">
-        <v>402</v>
-      </c>
-      <c r="L2" t="n">
-        <v>457</v>
-      </c>
-      <c r="M2" t="n">
-        <v>428.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>9.761659694949419</v>
-      </c>
-      <c r="O2" t="n">
-        <v>412</v>
-      </c>
-      <c r="P2" t="n">
-        <v>442</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>360.2</v>
-      </c>
-      <c r="R2" t="n">
-        <v>128.5050971751704</v>
-      </c>
-      <c r="S2" t="n">
+      <c r="AB2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>20.75957610357205</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>99</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>51.9539218923846</v>
+      </c>
+      <c r="AI2" t="n">
         <v>102</v>
       </c>
-      <c r="T2" t="n">
-        <v>439</v>
-      </c>
-      <c r="U2" t="n">
-        <v>394.8</v>
-      </c>
-      <c r="V2" t="n">
-        <v>96.93791827762757</v>
-      </c>
-      <c r="W2" t="n">
-        <v>105</v>
-      </c>
-      <c r="X2" t="n">
-        <v>443</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>267.4</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>162.5996309958912</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AJ2" t="n">
+        <v>276</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>39.5506005011302</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>234</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>121.3</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>27.83540910423269</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>101</v>
       </c>
-      <c r="AB2" t="n">
-        <v>445</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>266.3</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>163.7968558916807</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AR2" t="n">
+        <v>168</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>130.7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>40.08752923291731</v>
+      </c>
+      <c r="AU2" t="n">
         <v>100</v>
       </c>
-      <c r="AF2" t="n">
-        <v>443</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>267.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>164.3733859236342</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>99</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>440</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>300</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>161.1291407536204</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>99</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>442</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>169.9</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>131.8639071163903</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>97</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>437</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>138.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>99.31168108535874</v>
-      </c>
-      <c r="AU2" t="n">
+      <c r="AV2" t="n">
+        <v>206</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>120.9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>28.77307769426135</v>
+      </c>
+      <c r="AY2" t="n">
         <v>98</v>
       </c>
-      <c r="AV2" t="n">
-        <v>436</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>134</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>99.70957827611147</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>96</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>433</v>
+        <v>176</v>
       </c>
       <c r="BA2" t="n">
-        <v>104.1</v>
+        <v>110.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.624952830020754</v>
+        <v>14.51516448408353</v>
       </c>
       <c r="BC2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="BD2" t="n">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="BE2" t="n">
-        <v>107</v>
+        <v>124.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>11.15347479487895</v>
+        <v>47.81683803849853</v>
       </c>
       <c r="BG2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="BH2" t="n">
-        <v>137</v>
+        <v>261</v>
       </c>
       <c r="BI2" t="n">
-        <v>103.1</v>
+        <v>133.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>4.482186966202994</v>
+        <v>39.21683312048539</v>
       </c>
       <c r="BK2" t="n">
         <v>97</v>
       </c>
       <c r="BL2" t="n">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="BM2" t="n">
-        <v>106.7</v>
+        <v>113.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.148983655857283</v>
+        <v>14.56193668438371</v>
       </c>
       <c r="BO2" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="BP2" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="BQ2" t="n">
-        <v>113.7</v>
+        <v>125.4</v>
       </c>
       <c r="BR2" t="n">
-        <v>11.33181362359971</v>
+        <v>49.51807750710845</v>
       </c>
       <c r="BS2" t="n">
         <v>99</v>
       </c>
       <c r="BT2" t="n">
-        <v>129</v>
+        <v>267</v>
       </c>
       <c r="BU2" t="n">
-        <v>121.4</v>
+        <v>113.9</v>
       </c>
       <c r="BV2" t="n">
-        <v>17.77188791321845</v>
+        <v>26.1283371074395</v>
       </c>
       <c r="BW2" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="BX2" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="BY2" t="n">
-        <v>123.6</v>
+        <v>170.6</v>
       </c>
       <c r="BZ2" t="n">
-        <v>25.78449146289296</v>
+        <v>132.3527105880344</v>
       </c>
       <c r="CA2" t="n">
         <v>98</v>
       </c>
       <c r="CB2" t="n">
+        <v>560</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>120.3</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>25.06411777821035</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>171</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>167.4980895413437</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>96</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>664</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>157.4428467730433</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>98</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>644</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>119</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>22.45439823286298</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>94</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>165</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>15.4819249449156</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>100</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>140</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>25.02578670092111</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>101</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>174</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>111.1</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>15.85212919452778</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>99</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>145</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>124</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>20.47437422731156</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>104</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>166</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>114</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>19.83935482821959</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>98</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>162</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>17.68191166135608</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>99</v>
+      </c>
+      <c r="DP2" t="n">
         <v>161</v>
       </c>
-      <c r="CC2" t="n">
-        <v>134.8</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>30.37696495701965</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>102</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>175</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>154.8</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>20.85569466596594</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>103</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>174</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>155.5</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>18.51620911525899</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>102</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>169</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>133.3</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>28.64280014244418</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>86</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>159</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>137.2</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>26.26708967510485</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>82</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>158</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>143.1</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>12.259282197584</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>117</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>152</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>124.3</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>19.24603855342704</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>93</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>150</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>12.57616793780999</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>111</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>148</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>114.9</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>13.41976154780703</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>93</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>140</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>118.5</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>9.82089608946149</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>98</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>135</v>
-      </c>
       <c r="DQ2" t="n">
-        <v>6122.400000000001</v>
+        <v>4233.4</v>
       </c>
     </row>
   </sheetData>

--- a/weights/baseline_results.xlsx
+++ b/weights/baseline_results.xlsx
@@ -1025,367 +1025,367 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124.5</v>
+        <v>401.7</v>
       </c>
       <c r="B2" t="n">
-        <v>17.70451919708638</v>
+        <v>127.8366535857381</v>
       </c>
       <c r="C2" t="n">
+        <v>215</v>
+      </c>
+      <c r="D2" t="n">
+        <v>510</v>
+      </c>
+      <c r="E2" t="n">
+        <v>349.7</v>
+      </c>
+      <c r="F2" t="n">
+        <v>137.5667474355631</v>
+      </c>
+      <c r="G2" t="n">
+        <v>210</v>
+      </c>
+      <c r="H2" t="n">
+        <v>534</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1580.3</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1513.900528436396</v>
+      </c>
+      <c r="K2" t="n">
+        <v>208</v>
+      </c>
+      <c r="L2" t="n">
+        <v>4005</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1297.7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1850.305599083568</v>
+      </c>
+      <c r="O2" t="n">
+        <v>191</v>
+      </c>
+      <c r="P2" t="n">
+        <v>6141</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>575.3</v>
+      </c>
+      <c r="R2" t="n">
+        <v>890.1296590946736</v>
+      </c>
+      <c r="S2" t="n">
+        <v>192</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3232</v>
+      </c>
+      <c r="U2" t="n">
+        <v>236.2</v>
+      </c>
+      <c r="V2" t="n">
+        <v>25.49039034616771</v>
+      </c>
+      <c r="W2" t="n">
+        <v>174</v>
+      </c>
+      <c r="X2" t="n">
+        <v>274</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>252.6</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>93.96084290809655</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>168</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>527</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>241.5</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>89.81898463019942</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>177</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>505</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>204.2</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>17.28467529344998</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>173</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>224</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>170.9</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>17.76203817133608</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>146</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>200</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>174.7</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>25.1716109933393</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>147</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>218</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>147.9</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>41.30242123653285</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>105</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>216</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>32.15415991749746</v>
+      </c>
+      <c r="AY2" t="n">
         <v>103</v>
       </c>
-      <c r="D2" t="n">
-        <v>163</v>
-      </c>
-      <c r="E2" t="n">
-        <v>118.6</v>
-      </c>
-      <c r="F2" t="n">
-        <v>15.02131818450032</v>
-      </c>
-      <c r="G2" t="n">
-        <v>101</v>
-      </c>
-      <c r="H2" t="n">
-        <v>144</v>
-      </c>
-      <c r="I2" t="n">
-        <v>124.9</v>
-      </c>
-      <c r="J2" t="n">
-        <v>19.10732843701599</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="AZ2" t="n">
+        <v>202</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>19.48050307358616</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>103</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>170</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>111.7</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>17.75415444339718</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>150</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>17.74401307483738</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>154</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>20.96759404414345</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>97</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>173</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>2.156385865284783</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>100</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>106</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>2.712931993250108</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>98</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>108</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>2.343074902771996</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>95</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>102</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>3.195309061734091</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>101.4</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="CI2" t="n">
         <v>99</v>
       </c>
-      <c r="L2" t="n">
-        <v>157</v>
-      </c>
-      <c r="M2" t="n">
-        <v>204</v>
-      </c>
-      <c r="N2" t="n">
-        <v>268.2189404199487</v>
-      </c>
-      <c r="O2" t="n">
-        <v>101</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1008</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>130.4</v>
-      </c>
-      <c r="R2" t="n">
-        <v>50.66201733054064</v>
-      </c>
-      <c r="S2" t="n">
-        <v>101</v>
-      </c>
-      <c r="T2" t="n">
-        <v>271</v>
-      </c>
-      <c r="U2" t="n">
-        <v>400.6</v>
-      </c>
-      <c r="V2" t="n">
-        <v>421.9889098068811</v>
-      </c>
-      <c r="W2" t="n">
+      <c r="CJ2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>99</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>2.449489742783178</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>95</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>104</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>3.822302970723279</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>93</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>106</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>3.487119154832539</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>92</v>
+      </c>
+      <c r="CV2" t="n">
         <v>102</v>
       </c>
-      <c r="X2" t="n">
-        <v>1104</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>225.8</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>272.5783557071251</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1031</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>107.8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>20.75957610357205</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="CW2" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="CX2" t="n">
+        <v>3.534119409414458</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>93</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>102</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>2.808914381037628</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>93</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>103</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>3.583294573433783</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>92</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>103</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>4.570557952810575</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>91</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>107</v>
+      </c>
+      <c r="DM2" t="n">
         <v>99</v>
       </c>
-      <c r="AF2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>128.3</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>51.9539218923846</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>102</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>276</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>115.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>39.5506005011302</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>234</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>121.3</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>27.83540910423269</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>101</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>168</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>130.7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>40.08752923291731</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>100</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>206</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>120.9</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>28.77307769426135</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>98</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>176</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>110.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.51516448408353</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>100</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>148</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>124.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>47.81683803849853</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>98</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>261</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>133.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>39.21683312048539</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>97</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>210</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>113.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>14.56193668438371</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>103</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>144</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>125.4</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>49.51807750710845</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>99</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>267</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>113.9</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>26.1283371074395</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>93</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>167</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>170.6</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>132.3527105880344</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>98</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>560</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>120.3</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>25.06411777821035</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>100</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>171</v>
-      </c>
-      <c r="CG2" t="n">
-        <v>166.7</v>
-      </c>
-      <c r="CH2" t="n">
-        <v>167.4980895413437</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>96</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>664</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>184.5</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>157.4428467730433</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>98</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>644</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>119</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>22.45439823286298</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>94</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>165</v>
-      </c>
-      <c r="CS2" t="n">
-        <v>116.1</v>
-      </c>
-      <c r="CT2" t="n">
-        <v>15.4819249449156</v>
-      </c>
-      <c r="CU2" t="n">
-        <v>100</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>140</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>123.1</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>25.02578670092111</v>
-      </c>
-      <c r="CY2" t="n">
-        <v>101</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>174</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>111.1</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>15.85212919452778</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>99</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>145</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>124</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>20.47437422731156</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>104</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>166</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>114</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>19.83935482821959</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>98</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>162</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>109.5</v>
-      </c>
       <c r="DN2" t="n">
-        <v>17.68191166135608</v>
+        <v>3.521363372331802</v>
       </c>
       <c r="DO2" t="n">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="DP2" t="n">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="DQ2" t="n">
-        <v>4233.4</v>
+        <v>7509.599999999999</v>
       </c>
     </row>
   </sheetData>
